--- a/templates/template_correc_carga.xlsx
+++ b/templates/template_correc_carga.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Developer user\android\williApp\EquiposUnidos\app\src\main\res\raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Developer user\android\williApp\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8614C2BC-4BD1-4837-A341-F60F22257FB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{993C09E0-557A-402E-92D5-378DD4868B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FT-MANT-11" sheetId="15" r:id="rId1"/>
@@ -31,15 +31,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="53">
   <si>
     <t>Código</t>
   </si>
   <si>
     <t>Fecha</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>Observaciones:</t>
@@ -202,7 +199,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="_-[$€-2]* #,##0.00_-;\-[$€-2]* #,##0.00_-;_-[$€-2]* &quot;-&quot;??_-"/>
+    <numFmt numFmtId="165" formatCode="_-[$€-2]* #,##0.00_-;\-[$€-2]* #,##0.00_-;_-[$€-2]* &quot;-&quot;??_-"/>
   </numFmts>
   <fonts count="33">
     <font>
@@ -534,7 +531,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="69">
+  <borders count="67">
     <border>
       <left/>
       <right/>
@@ -980,19 +977,6 @@
       <left style="thin">
         <color theme="0"/>
       </left>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
       <right/>
       <top/>
       <bottom style="medium">
@@ -1215,43 +1199,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -1363,6 +1310,30 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -1401,7 +1372,7 @@
     <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1431,7 +1402,7 @@
   </cellStyleXfs>
   <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
@@ -1448,17 +1419,14 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="22" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1469,23 +1437,14 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="30" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1493,24 +1452,108 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1523,9 +1566,6 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1547,10 +1587,65 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
@@ -1558,11 +1653,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
@@ -1578,10 +1669,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
@@ -1610,10 +1697,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="25" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1622,7 +1709,7 @@
     <xf numFmtId="0" fontId="24" fillId="25" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1643,164 +1730,48 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="60">
@@ -1925,8 +1896,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="595313" y="35719"/>
-          <a:ext cx="2171700" cy="783312"/>
+          <a:off x="619125" y="35719"/>
+          <a:ext cx="2164080" cy="787122"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2646,958 +2617,931 @@
   <dimension ref="B1:G95"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="6.88671875" style="10" customWidth="1"/>
-    <col min="2" max="2" width="35.109375" style="10" customWidth="1"/>
-    <col min="3" max="3" width="49.109375" style="10" customWidth="1"/>
-    <col min="4" max="4" width="17.77734375" style="10" customWidth="1"/>
-    <col min="5" max="5" width="11.88671875" style="10" customWidth="1"/>
-    <col min="6" max="6" width="34.6640625" style="10" customWidth="1"/>
-    <col min="7" max="7" width="29.44140625" style="10" customWidth="1"/>
-    <col min="8" max="16384" width="11.44140625" style="10"/>
+    <col min="1" max="1" width="6.88671875" style="9" customWidth="1"/>
+    <col min="2" max="2" width="35.109375" style="9" customWidth="1"/>
+    <col min="3" max="3" width="49.109375" style="9" customWidth="1"/>
+    <col min="4" max="4" width="17.77734375" style="9" customWidth="1"/>
+    <col min="5" max="5" width="11.88671875" style="9" customWidth="1"/>
+    <col min="6" max="6" width="34.6640625" style="9" customWidth="1"/>
+    <col min="7" max="7" width="29.44140625" style="9" customWidth="1"/>
+    <col min="8" max="16384" width="11.44140625" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" s="3" customFormat="1" ht="22.5" customHeight="1">
-      <c r="B1" s="40"/>
-      <c r="C1" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="D1" s="44"/>
-      <c r="E1" s="45"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="83" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="84"/>
+      <c r="E1" s="85"/>
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="2:7" s="3" customFormat="1" ht="22.5" customHeight="1">
-      <c r="B2" s="41"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="48"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="112"/>
+      <c r="E2" s="87"/>
       <c r="F2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="11">
+        <v>25</v>
+      </c>
+      <c r="G2" s="10">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="2:7" s="3" customFormat="1" ht="22.5" customHeight="1">
-      <c r="B3" s="42"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="90"/>
       <c r="F3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="12">
+      <c r="G3" s="11">
         <v>45154</v>
       </c>
     </row>
     <row r="4" spans="2:7" s="3" customFormat="1" ht="22.5" customHeight="1">
-      <c r="B4" s="52"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="54"/>
+      <c r="B4" s="91"/>
+      <c r="C4" s="92"/>
+      <c r="D4" s="92"/>
+      <c r="E4" s="92"/>
+      <c r="F4" s="92"/>
+      <c r="G4" s="93"/>
     </row>
     <row r="5" spans="2:7" s="3" customFormat="1" ht="33" customHeight="1">
       <c r="B5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="7"/>
+      <c r="D5" s="103" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="64" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="65"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="55" t="s">
-        <v>6</v>
+      <c r="E5" s="104"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="94" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="2:7" s="3" customFormat="1" ht="33" customHeight="1">
       <c r="B6" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6" s="7"/>
-      <c r="D6" s="64" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="65"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="55"/>
+      <c r="D6" s="103" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="104"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="94"/>
     </row>
     <row r="7" spans="2:7" s="3" customFormat="1" ht="33" customHeight="1">
       <c r="B7" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" s="7"/>
-      <c r="D7" s="64" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="65"/>
-      <c r="F7" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7" s="66"/>
+      <c r="D7" s="103" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="104"/>
+      <c r="F7" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="70"/>
     </row>
     <row r="8" spans="2:7" s="3" customFormat="1" ht="33" customHeight="1">
       <c r="B8" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8" s="7"/>
-      <c r="D8" s="69" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="70"/>
-      <c r="F8" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="G8" s="67"/>
+      <c r="D8" s="73" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="74"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="71"/>
     </row>
     <row r="9" spans="2:7" s="3" customFormat="1" ht="42" customHeight="1" thickBot="1">
       <c r="B9" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="98"/>
+      <c r="E9" s="99"/>
+      <c r="F9" s="100"/>
+      <c r="G9" s="72"/>
+    </row>
+    <row r="10" spans="2:7" s="3" customFormat="1" ht="33" customHeight="1">
+      <c r="B10" s="75" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="76"/>
+      <c r="D10" s="76"/>
+      <c r="E10" s="76"/>
+      <c r="F10" s="76"/>
+      <c r="G10" s="77"/>
+    </row>
+    <row r="11" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B11" s="101" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="102"/>
+      <c r="D11" s="102"/>
+      <c r="E11" s="102"/>
+      <c r="F11" s="102"/>
+      <c r="G11" s="113"/>
+    </row>
+    <row r="12" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B12" s="101" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="102"/>
+      <c r="D12" s="102"/>
+      <c r="E12" s="102"/>
+      <c r="F12" s="102"/>
+      <c r="G12" s="113"/>
+    </row>
+    <row r="13" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B13" s="101" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="102"/>
+      <c r="D13" s="102"/>
+      <c r="E13" s="102"/>
+      <c r="F13" s="102"/>
+      <c r="G13" s="113"/>
+    </row>
+    <row r="14" spans="2:7" s="3" customFormat="1" ht="33" customHeight="1" thickBot="1">
+      <c r="B14" s="78" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="79"/>
+      <c r="D14" s="108" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" s="95" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="96"/>
+      <c r="G14" s="97"/>
+    </row>
+    <row r="15" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B15" s="59" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="60"/>
+      <c r="D15" s="109"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="52"/>
+      <c r="G15" s="53"/>
+    </row>
+    <row r="16" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B16" s="61"/>
+      <c r="C16" s="114"/>
+      <c r="D16" s="110"/>
+      <c r="E16" s="107"/>
+      <c r="F16" s="107"/>
+      <c r="G16" s="55"/>
+    </row>
+    <row r="17" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B17" s="61"/>
+      <c r="C17" s="114"/>
+      <c r="D17" s="110"/>
+      <c r="E17" s="107"/>
+      <c r="F17" s="107"/>
+      <c r="G17" s="55"/>
+    </row>
+    <row r="18" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B18" s="61"/>
+      <c r="C18" s="114"/>
+      <c r="D18" s="110"/>
+      <c r="E18" s="107"/>
+      <c r="F18" s="107"/>
+      <c r="G18" s="55"/>
+    </row>
+    <row r="19" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
+      <c r="B19" s="61"/>
+      <c r="C19" s="114"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="58"/>
+    </row>
+    <row r="20" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B20" s="59" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="60"/>
+      <c r="D20" s="109"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="52"/>
+      <c r="G20" s="53"/>
+    </row>
+    <row r="21" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B21" s="61"/>
+      <c r="C21" s="114"/>
+      <c r="D21" s="110"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="107"/>
+      <c r="G21" s="55"/>
+    </row>
+    <row r="22" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B22" s="61"/>
+      <c r="C22" s="114"/>
+      <c r="D22" s="110"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="107"/>
+      <c r="G22" s="55"/>
+    </row>
+    <row r="23" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B23" s="61"/>
+      <c r="C23" s="114"/>
+      <c r="D23" s="110"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="107"/>
+      <c r="G23" s="55"/>
+    </row>
+    <row r="24" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
+      <c r="B24" s="61"/>
+      <c r="C24" s="114"/>
+      <c r="D24" s="111"/>
+      <c r="E24" s="56"/>
+      <c r="F24" s="57"/>
+      <c r="G24" s="58"/>
+    </row>
+    <row r="25" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B25" s="59" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" s="60"/>
+      <c r="D25" s="109"/>
+      <c r="E25" s="51"/>
+      <c r="F25" s="52"/>
+      <c r="G25" s="53"/>
+    </row>
+    <row r="26" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B26" s="61"/>
+      <c r="C26" s="114"/>
+      <c r="D26" s="110"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="107"/>
+      <c r="G26" s="55"/>
+    </row>
+    <row r="27" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B27" s="61"/>
+      <c r="C27" s="114"/>
+      <c r="D27" s="110"/>
+      <c r="E27" s="54"/>
+      <c r="F27" s="107"/>
+      <c r="G27" s="55"/>
+    </row>
+    <row r="28" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B28" s="61"/>
+      <c r="C28" s="114"/>
+      <c r="D28" s="110"/>
+      <c r="E28" s="54"/>
+      <c r="F28" s="107"/>
+      <c r="G28" s="55"/>
+    </row>
+    <row r="29" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
+      <c r="B29" s="61"/>
+      <c r="C29" s="114"/>
+      <c r="D29" s="111"/>
+      <c r="E29" s="56"/>
+      <c r="F29" s="57"/>
+      <c r="G29" s="58"/>
+    </row>
+    <row r="30" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B30" s="59" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="60"/>
+      <c r="D30" s="109"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="52"/>
+      <c r="G30" s="53"/>
+    </row>
+    <row r="31" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B31" s="61"/>
+      <c r="C31" s="114"/>
+      <c r="D31" s="110"/>
+      <c r="E31" s="54"/>
+      <c r="F31" s="107"/>
+      <c r="G31" s="55"/>
+    </row>
+    <row r="32" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B32" s="61"/>
+      <c r="C32" s="114"/>
+      <c r="D32" s="110"/>
+      <c r="E32" s="54"/>
+      <c r="F32" s="107"/>
+      <c r="G32" s="55"/>
+    </row>
+    <row r="33" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B33" s="61"/>
+      <c r="C33" s="114"/>
+      <c r="D33" s="110"/>
+      <c r="E33" s="54"/>
+      <c r="F33" s="107"/>
+      <c r="G33" s="55"/>
+    </row>
+    <row r="34" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
+      <c r="B34" s="61"/>
+      <c r="C34" s="114"/>
+      <c r="D34" s="111"/>
+      <c r="E34" s="56"/>
+      <c r="F34" s="57"/>
+      <c r="G34" s="58"/>
+    </row>
+    <row r="35" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B35" s="59" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="60"/>
+      <c r="D35" s="109"/>
+      <c r="E35" s="51"/>
+      <c r="F35" s="52"/>
+      <c r="G35" s="53"/>
+    </row>
+    <row r="36" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B36" s="61"/>
+      <c r="C36" s="114"/>
+      <c r="D36" s="110"/>
+      <c r="E36" s="54"/>
+      <c r="F36" s="107"/>
+      <c r="G36" s="55"/>
+    </row>
+    <row r="37" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B37" s="61"/>
+      <c r="C37" s="114"/>
+      <c r="D37" s="110"/>
+      <c r="E37" s="54"/>
+      <c r="F37" s="107"/>
+      <c r="G37" s="55"/>
+    </row>
+    <row r="38" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B38" s="61"/>
+      <c r="C38" s="114"/>
+      <c r="D38" s="110"/>
+      <c r="E38" s="54"/>
+      <c r="F38" s="107"/>
+      <c r="G38" s="55"/>
+    </row>
+    <row r="39" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
+      <c r="B39" s="61"/>
+      <c r="C39" s="114"/>
+      <c r="D39" s="111"/>
+      <c r="E39" s="56"/>
+      <c r="F39" s="57"/>
+      <c r="G39" s="58"/>
+    </row>
+    <row r="40" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B40" s="59" t="s">
+        <v>17</v>
+      </c>
+      <c r="C40" s="60"/>
+      <c r="D40" s="109"/>
+      <c r="E40" s="51"/>
+      <c r="F40" s="52"/>
+      <c r="G40" s="53"/>
+    </row>
+    <row r="41" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B41" s="61"/>
+      <c r="C41" s="114"/>
+      <c r="D41" s="110"/>
+      <c r="E41" s="54"/>
+      <c r="F41" s="107"/>
+      <c r="G41" s="55"/>
+    </row>
+    <row r="42" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B42" s="61"/>
+      <c r="C42" s="114"/>
+      <c r="D42" s="110"/>
+      <c r="E42" s="54"/>
+      <c r="F42" s="107"/>
+      <c r="G42" s="55"/>
+    </row>
+    <row r="43" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B43" s="61"/>
+      <c r="C43" s="114"/>
+      <c r="D43" s="110"/>
+      <c r="E43" s="54"/>
+      <c r="F43" s="107"/>
+      <c r="G43" s="55"/>
+    </row>
+    <row r="44" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
+      <c r="B44" s="61"/>
+      <c r="C44" s="114"/>
+      <c r="D44" s="111"/>
+      <c r="E44" s="56"/>
+      <c r="F44" s="57"/>
+      <c r="G44" s="58"/>
+    </row>
+    <row r="45" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B45" s="59" t="s">
+        <v>26</v>
+      </c>
+      <c r="C45" s="60"/>
+      <c r="D45" s="109"/>
+      <c r="E45" s="51"/>
+      <c r="F45" s="52"/>
+      <c r="G45" s="53"/>
+    </row>
+    <row r="46" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B46" s="61"/>
+      <c r="C46" s="114"/>
+      <c r="D46" s="110"/>
+      <c r="E46" s="54"/>
+      <c r="F46" s="107"/>
+      <c r="G46" s="55"/>
+    </row>
+    <row r="47" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B47" s="61"/>
+      <c r="C47" s="114"/>
+      <c r="D47" s="110"/>
+      <c r="E47" s="54"/>
+      <c r="F47" s="107"/>
+      <c r="G47" s="55"/>
+    </row>
+    <row r="48" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B48" s="61"/>
+      <c r="C48" s="114"/>
+      <c r="D48" s="110"/>
+      <c r="E48" s="54"/>
+      <c r="F48" s="107"/>
+      <c r="G48" s="55"/>
+    </row>
+    <row r="49" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
+      <c r="B49" s="61"/>
+      <c r="C49" s="114"/>
+      <c r="D49" s="111"/>
+      <c r="E49" s="56"/>
+      <c r="F49" s="57"/>
+      <c r="G49" s="58"/>
+    </row>
+    <row r="50" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B50" s="59" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="60"/>
+      <c r="D50" s="109"/>
+      <c r="E50" s="51"/>
+      <c r="F50" s="52"/>
+      <c r="G50" s="53"/>
+    </row>
+    <row r="51" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B51" s="61"/>
+      <c r="C51" s="114"/>
+      <c r="D51" s="110"/>
+      <c r="E51" s="54"/>
+      <c r="F51" s="107"/>
+      <c r="G51" s="55"/>
+    </row>
+    <row r="52" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B52" s="61"/>
+      <c r="C52" s="114"/>
+      <c r="D52" s="110"/>
+      <c r="E52" s="54"/>
+      <c r="F52" s="107"/>
+      <c r="G52" s="55"/>
+    </row>
+    <row r="53" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B53" s="61"/>
+      <c r="C53" s="114"/>
+      <c r="D53" s="110"/>
+      <c r="E53" s="54"/>
+      <c r="F53" s="107"/>
+      <c r="G53" s="55"/>
+    </row>
+    <row r="54" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
+      <c r="B54" s="61"/>
+      <c r="C54" s="114"/>
+      <c r="D54" s="111"/>
+      <c r="E54" s="56"/>
+      <c r="F54" s="57"/>
+      <c r="G54" s="58"/>
+    </row>
+    <row r="55" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B55" s="59" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55" s="60"/>
+      <c r="D55" s="109"/>
+      <c r="E55" s="51"/>
+      <c r="F55" s="52"/>
+      <c r="G55" s="53"/>
+    </row>
+    <row r="56" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B56" s="61"/>
+      <c r="C56" s="114"/>
+      <c r="D56" s="110"/>
+      <c r="E56" s="54"/>
+      <c r="F56" s="107"/>
+      <c r="G56" s="55"/>
+    </row>
+    <row r="57" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B57" s="61"/>
+      <c r="C57" s="114"/>
+      <c r="D57" s="110"/>
+      <c r="E57" s="54"/>
+      <c r="F57" s="107"/>
+      <c r="G57" s="55"/>
+    </row>
+    <row r="58" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B58" s="61"/>
+      <c r="C58" s="114"/>
+      <c r="D58" s="110"/>
+      <c r="E58" s="54"/>
+      <c r="F58" s="107"/>
+      <c r="G58" s="55"/>
+    </row>
+    <row r="59" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
+      <c r="B59" s="61"/>
+      <c r="C59" s="114"/>
+      <c r="D59" s="111"/>
+      <c r="E59" s="56"/>
+      <c r="F59" s="57"/>
+      <c r="G59" s="58"/>
+    </row>
+    <row r="60" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B60" s="59" t="s">
+        <v>30</v>
+      </c>
+      <c r="C60" s="60"/>
+      <c r="D60" s="109"/>
+      <c r="E60" s="51"/>
+      <c r="F60" s="52"/>
+      <c r="G60" s="53"/>
+    </row>
+    <row r="61" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B61" s="61"/>
+      <c r="C61" s="114"/>
+      <c r="D61" s="110"/>
+      <c r="E61" s="54"/>
+      <c r="F61" s="107"/>
+      <c r="G61" s="55"/>
+    </row>
+    <row r="62" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B62" s="61"/>
+      <c r="C62" s="114"/>
+      <c r="D62" s="110"/>
+      <c r="E62" s="54"/>
+      <c r="F62" s="107"/>
+      <c r="G62" s="55"/>
+    </row>
+    <row r="63" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B63" s="61"/>
+      <c r="C63" s="114"/>
+      <c r="D63" s="110"/>
+      <c r="E63" s="54"/>
+      <c r="F63" s="107"/>
+      <c r="G63" s="55"/>
+    </row>
+    <row r="64" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
+      <c r="B64" s="61"/>
+      <c r="C64" s="114"/>
+      <c r="D64" s="111"/>
+      <c r="E64" s="56"/>
+      <c r="F64" s="57"/>
+      <c r="G64" s="58"/>
+    </row>
+    <row r="65" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B65" s="64" t="s">
+        <v>51</v>
+      </c>
+      <c r="C65" s="65"/>
+      <c r="D65" s="109"/>
+      <c r="E65" s="51"/>
+      <c r="F65" s="52"/>
+      <c r="G65" s="53"/>
+    </row>
+    <row r="66" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B66" s="66"/>
+      <c r="C66" s="115"/>
+      <c r="D66" s="110"/>
+      <c r="E66" s="54"/>
+      <c r="F66" s="107"/>
+      <c r="G66" s="55"/>
+    </row>
+    <row r="67" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B67" s="66"/>
+      <c r="C67" s="115"/>
+      <c r="D67" s="110"/>
+      <c r="E67" s="54"/>
+      <c r="F67" s="107"/>
+      <c r="G67" s="55"/>
+    </row>
+    <row r="68" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B68" s="66"/>
+      <c r="C68" s="115"/>
+      <c r="D68" s="110"/>
+      <c r="E68" s="54"/>
+      <c r="F68" s="107"/>
+      <c r="G68" s="55"/>
+    </row>
+    <row r="69" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
+      <c r="B69" s="66"/>
+      <c r="C69" s="115"/>
+      <c r="D69" s="111"/>
+      <c r="E69" s="56"/>
+      <c r="F69" s="57"/>
+      <c r="G69" s="58"/>
+    </row>
+    <row r="70" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B70" s="59" t="s">
+        <v>12</v>
+      </c>
+      <c r="C70" s="60"/>
+      <c r="D70" s="109"/>
+      <c r="E70" s="51"/>
+      <c r="F70" s="52"/>
+      <c r="G70" s="53"/>
+    </row>
+    <row r="71" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B71" s="61"/>
+      <c r="C71" s="114"/>
+      <c r="D71" s="110"/>
+      <c r="E71" s="54"/>
+      <c r="F71" s="107"/>
+      <c r="G71" s="55"/>
+    </row>
+    <row r="72" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B72" s="61"/>
+      <c r="C72" s="114"/>
+      <c r="D72" s="110"/>
+      <c r="E72" s="54"/>
+      <c r="F72" s="107"/>
+      <c r="G72" s="55"/>
+    </row>
+    <row r="73" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
+      <c r="B73" s="61"/>
+      <c r="C73" s="114"/>
+      <c r="D73" s="110"/>
+      <c r="E73" s="54"/>
+      <c r="F73" s="107"/>
+      <c r="G73" s="55"/>
+    </row>
+    <row r="74" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
+      <c r="B74" s="62"/>
+      <c r="C74" s="63"/>
+      <c r="D74" s="111"/>
+      <c r="E74" s="56"/>
+      <c r="F74" s="57"/>
+      <c r="G74" s="58"/>
+    </row>
+    <row r="75" spans="2:7" ht="30" customHeight="1" thickBot="1">
+      <c r="B75" s="116" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="59"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="61"/>
-      <c r="G9" s="68"/>
-    </row>
-    <row r="10" spans="2:7" s="3" customFormat="1" ht="33" customHeight="1">
-      <c r="B10" s="71" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="72"/>
-      <c r="D10" s="72"/>
-      <c r="E10" s="72"/>
-      <c r="F10" s="72"/>
-      <c r="G10" s="73"/>
-    </row>
-    <row r="11" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B11" s="62" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="63"/>
-      <c r="D11" s="63"/>
-      <c r="E11" s="63"/>
-      <c r="F11" s="63"/>
-      <c r="G11" s="18"/>
-    </row>
-    <row r="12" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B12" s="62" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="63"/>
-      <c r="D12" s="63"/>
-      <c r="E12" s="63"/>
-      <c r="F12" s="63"/>
-      <c r="G12" s="18"/>
-    </row>
-    <row r="13" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B13" s="62" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="63"/>
-      <c r="D13" s="63"/>
-      <c r="E13" s="63"/>
-      <c r="F13" s="63"/>
-      <c r="G13" s="18"/>
-    </row>
-    <row r="14" spans="2:7" s="3" customFormat="1" ht="33" customHeight="1" thickBot="1">
-      <c r="B14" s="74" t="s">
-        <v>4</v>
-      </c>
-      <c r="C14" s="75"/>
-      <c r="D14" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="E14" s="56" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="57"/>
-      <c r="G14" s="58"/>
-    </row>
-    <row r="15" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B15" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="37"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="29"/>
-    </row>
-    <row r="16" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B16" s="38"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="32"/>
-    </row>
-    <row r="17" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B17" s="38"/>
-      <c r="C17" s="39"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="32"/>
-    </row>
-    <row r="18" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B18" s="38"/>
-      <c r="C18" s="39"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="32"/>
-    </row>
-    <row r="19" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
-      <c r="B19" s="38"/>
-      <c r="C19" s="39"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="35"/>
-    </row>
-    <row r="20" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B20" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="37"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="29"/>
-    </row>
-    <row r="21" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B21" s="38"/>
-      <c r="C21" s="39"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="32"/>
-    </row>
-    <row r="22" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B22" s="38"/>
-      <c r="C22" s="39"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="32"/>
-    </row>
-    <row r="23" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B23" s="38"/>
-      <c r="C23" s="39"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="32"/>
-    </row>
-    <row r="24" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
-      <c r="B24" s="38"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="35"/>
-    </row>
-    <row r="25" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B25" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" s="37"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="29"/>
-    </row>
-    <row r="26" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B26" s="38"/>
-      <c r="C26" s="39"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="32"/>
-    </row>
-    <row r="27" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B27" s="38"/>
-      <c r="C27" s="39"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="31"/>
-      <c r="G27" s="32"/>
-    </row>
-    <row r="28" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B28" s="38"/>
-      <c r="C28" s="39"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="30"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="32"/>
-    </row>
-    <row r="29" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
-      <c r="B29" s="38"/>
-      <c r="C29" s="39"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="34"/>
-      <c r="G29" s="35"/>
-    </row>
-    <row r="30" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B30" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="C30" s="37"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="29"/>
-    </row>
-    <row r="31" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B31" s="38"/>
-      <c r="C31" s="39"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="31"/>
-      <c r="G31" s="32"/>
-    </row>
-    <row r="32" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B32" s="38"/>
-      <c r="C32" s="39"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="32"/>
-    </row>
-    <row r="33" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B33" s="38"/>
-      <c r="C33" s="39"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="31"/>
-      <c r="G33" s="32"/>
-    </row>
-    <row r="34" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
-      <c r="B34" s="38"/>
-      <c r="C34" s="39"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="33"/>
-      <c r="F34" s="34"/>
-      <c r="G34" s="35"/>
-    </row>
-    <row r="35" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B35" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="C35" s="37"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="27"/>
-      <c r="F35" s="28"/>
-      <c r="G35" s="29"/>
-    </row>
-    <row r="36" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B36" s="38"/>
-      <c r="C36" s="39"/>
-      <c r="D36" s="22"/>
-      <c r="E36" s="30"/>
-      <c r="F36" s="31"/>
-      <c r="G36" s="32"/>
-    </row>
-    <row r="37" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B37" s="38"/>
-      <c r="C37" s="39"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="30"/>
-      <c r="F37" s="31"/>
-      <c r="G37" s="32"/>
-    </row>
-    <row r="38" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B38" s="38"/>
-      <c r="C38" s="39"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="30"/>
-      <c r="F38" s="31"/>
-      <c r="G38" s="32"/>
-    </row>
-    <row r="39" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
-      <c r="B39" s="38"/>
-      <c r="C39" s="39"/>
-      <c r="D39" s="23"/>
-      <c r="E39" s="33"/>
-      <c r="F39" s="34"/>
-      <c r="G39" s="35"/>
-    </row>
-    <row r="40" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B40" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="C40" s="37"/>
-      <c r="D40" s="21"/>
-      <c r="E40" s="27"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="29"/>
-    </row>
-    <row r="41" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B41" s="38"/>
-      <c r="C41" s="39"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="30"/>
-      <c r="F41" s="31"/>
-      <c r="G41" s="32"/>
-    </row>
-    <row r="42" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B42" s="38"/>
-      <c r="C42" s="39"/>
-      <c r="D42" s="22"/>
-      <c r="E42" s="30"/>
-      <c r="F42" s="31"/>
-      <c r="G42" s="32"/>
-    </row>
-    <row r="43" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B43" s="38"/>
-      <c r="C43" s="39"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="30"/>
-      <c r="F43" s="31"/>
-      <c r="G43" s="32"/>
-    </row>
-    <row r="44" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
-      <c r="B44" s="38"/>
-      <c r="C44" s="39"/>
-      <c r="D44" s="23"/>
-      <c r="E44" s="33"/>
-      <c r="F44" s="34"/>
-      <c r="G44" s="35"/>
-    </row>
-    <row r="45" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B45" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="C45" s="37"/>
-      <c r="D45" s="21"/>
-      <c r="E45" s="27"/>
-      <c r="F45" s="28"/>
-      <c r="G45" s="29"/>
-    </row>
-    <row r="46" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B46" s="38"/>
-      <c r="C46" s="39"/>
-      <c r="D46" s="22"/>
-      <c r="E46" s="30"/>
-      <c r="F46" s="31"/>
-      <c r="G46" s="32"/>
-    </row>
-    <row r="47" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B47" s="38"/>
-      <c r="C47" s="39"/>
-      <c r="D47" s="22"/>
-      <c r="E47" s="30"/>
-      <c r="F47" s="31"/>
-      <c r="G47" s="32"/>
-    </row>
-    <row r="48" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B48" s="38"/>
-      <c r="C48" s="39"/>
-      <c r="D48" s="22"/>
-      <c r="E48" s="30"/>
-      <c r="F48" s="31"/>
-      <c r="G48" s="32"/>
-    </row>
-    <row r="49" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
-      <c r="B49" s="38"/>
-      <c r="C49" s="39"/>
-      <c r="D49" s="23"/>
-      <c r="E49" s="33"/>
-      <c r="F49" s="34"/>
-      <c r="G49" s="35"/>
-    </row>
-    <row r="50" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B50" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="C50" s="37"/>
-      <c r="D50" s="21"/>
-      <c r="E50" s="27"/>
-      <c r="F50" s="28"/>
-      <c r="G50" s="29"/>
-    </row>
-    <row r="51" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B51" s="38"/>
-      <c r="C51" s="39"/>
-      <c r="D51" s="22"/>
-      <c r="E51" s="30"/>
-      <c r="F51" s="31"/>
-      <c r="G51" s="32"/>
-    </row>
-    <row r="52" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B52" s="38"/>
-      <c r="C52" s="39"/>
-      <c r="D52" s="22"/>
-      <c r="E52" s="30"/>
-      <c r="F52" s="31"/>
-      <c r="G52" s="32"/>
-    </row>
-    <row r="53" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B53" s="38"/>
-      <c r="C53" s="39"/>
-      <c r="D53" s="22"/>
-      <c r="E53" s="30"/>
-      <c r="F53" s="31"/>
-      <c r="G53" s="32"/>
-    </row>
-    <row r="54" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
-      <c r="B54" s="38"/>
-      <c r="C54" s="39"/>
-      <c r="D54" s="23"/>
-      <c r="E54" s="33"/>
-      <c r="F54" s="34"/>
-      <c r="G54" s="35"/>
-    </row>
-    <row r="55" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B55" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="C55" s="37"/>
-      <c r="D55" s="21"/>
-      <c r="E55" s="27"/>
-      <c r="F55" s="28"/>
-      <c r="G55" s="29"/>
-    </row>
-    <row r="56" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B56" s="38"/>
-      <c r="C56" s="39"/>
-      <c r="D56" s="22"/>
-      <c r="E56" s="30"/>
-      <c r="F56" s="31"/>
-      <c r="G56" s="32"/>
-    </row>
-    <row r="57" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B57" s="38"/>
-      <c r="C57" s="39"/>
-      <c r="D57" s="22"/>
-      <c r="E57" s="30"/>
-      <c r="F57" s="31"/>
-      <c r="G57" s="32"/>
-    </row>
-    <row r="58" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B58" s="38"/>
-      <c r="C58" s="39"/>
-      <c r="D58" s="22"/>
-      <c r="E58" s="30"/>
-      <c r="F58" s="31"/>
-      <c r="G58" s="32"/>
-    </row>
-    <row r="59" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
-      <c r="B59" s="38"/>
-      <c r="C59" s="39"/>
-      <c r="D59" s="23"/>
-      <c r="E59" s="33"/>
-      <c r="F59" s="34"/>
-      <c r="G59" s="35"/>
-    </row>
-    <row r="60" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B60" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="37"/>
-      <c r="D60" s="21"/>
-      <c r="E60" s="27"/>
-      <c r="F60" s="28"/>
-      <c r="G60" s="29"/>
-    </row>
-    <row r="61" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B61" s="38"/>
-      <c r="C61" s="39"/>
-      <c r="D61" s="22"/>
-      <c r="E61" s="30"/>
-      <c r="F61" s="31"/>
-      <c r="G61" s="32"/>
-    </row>
-    <row r="62" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B62" s="38"/>
-      <c r="C62" s="39"/>
-      <c r="D62" s="22"/>
-      <c r="E62" s="30"/>
-      <c r="F62" s="31"/>
-      <c r="G62" s="32"/>
-    </row>
-    <row r="63" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B63" s="38"/>
-      <c r="C63" s="39"/>
-      <c r="D63" s="22"/>
-      <c r="E63" s="30"/>
-      <c r="F63" s="31"/>
-      <c r="G63" s="32"/>
-    </row>
-    <row r="64" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
-      <c r="B64" s="38"/>
-      <c r="C64" s="39"/>
-      <c r="D64" s="23"/>
-      <c r="E64" s="33"/>
-      <c r="F64" s="34"/>
-      <c r="G64" s="35"/>
-    </row>
-    <row r="65" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B65" s="84" t="s">
+      <c r="C75" s="105"/>
+      <c r="D75" s="106"/>
+      <c r="E75" s="106"/>
+      <c r="F75" s="106"/>
+      <c r="G75" s="117"/>
+    </row>
+    <row r="76" spans="2:7" ht="30" customHeight="1">
+      <c r="B76" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C76" s="31"/>
+      <c r="D76" s="31"/>
+      <c r="E76" s="67" t="s">
+        <v>37</v>
+      </c>
+      <c r="F76" s="68"/>
+      <c r="G76" s="69"/>
+    </row>
+    <row r="77" spans="2:7" ht="30" customHeight="1">
+      <c r="B77" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C77" s="31"/>
+      <c r="D77" s="31"/>
+      <c r="E77" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="F77" s="33"/>
+      <c r="G77" s="34"/>
+    </row>
+    <row r="78" spans="2:7" ht="30" customHeight="1">
+      <c r="B78" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C65" s="85"/>
-      <c r="D65" s="21"/>
-      <c r="E65" s="27"/>
-      <c r="F65" s="28"/>
-      <c r="G65" s="29"/>
-    </row>
-    <row r="66" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B66" s="86"/>
-      <c r="C66" s="87"/>
-      <c r="D66" s="22"/>
-      <c r="E66" s="30"/>
-      <c r="F66" s="31"/>
-      <c r="G66" s="32"/>
-    </row>
-    <row r="67" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B67" s="86"/>
-      <c r="C67" s="87"/>
-      <c r="D67" s="22"/>
-      <c r="E67" s="30"/>
-      <c r="F67" s="31"/>
-      <c r="G67" s="32"/>
-    </row>
-    <row r="68" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B68" s="86"/>
-      <c r="C68" s="87"/>
-      <c r="D68" s="22"/>
-      <c r="E68" s="30"/>
-      <c r="F68" s="31"/>
-      <c r="G68" s="32"/>
-    </row>
-    <row r="69" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
-      <c r="B69" s="86"/>
-      <c r="C69" s="87"/>
-      <c r="D69" s="23"/>
-      <c r="E69" s="33"/>
-      <c r="F69" s="34"/>
-      <c r="G69" s="35"/>
-    </row>
-    <row r="70" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B70" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="C70" s="37"/>
-      <c r="D70" s="21"/>
-      <c r="E70" s="27"/>
-      <c r="F70" s="28"/>
-      <c r="G70" s="29"/>
-    </row>
-    <row r="71" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B71" s="38"/>
-      <c r="C71" s="39"/>
-      <c r="D71" s="22"/>
-      <c r="E71" s="30"/>
-      <c r="F71" s="31"/>
-      <c r="G71" s="32"/>
-    </row>
-    <row r="72" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B72" s="38"/>
-      <c r="C72" s="39"/>
-      <c r="D72" s="22"/>
-      <c r="E72" s="30"/>
-      <c r="F72" s="31"/>
-      <c r="G72" s="32"/>
-    </row>
-    <row r="73" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1">
-      <c r="B73" s="38"/>
-      <c r="C73" s="39"/>
-      <c r="D73" s="22"/>
-      <c r="E73" s="30"/>
-      <c r="F73" s="31"/>
-      <c r="G73" s="32"/>
-    </row>
-    <row r="74" spans="2:7" s="3" customFormat="1" ht="21" customHeight="1" thickBot="1">
-      <c r="B74" s="82"/>
-      <c r="C74" s="83"/>
-      <c r="D74" s="23"/>
-      <c r="E74" s="33"/>
-      <c r="F74" s="34"/>
-      <c r="G74" s="35"/>
-    </row>
-    <row r="75" spans="2:7" ht="30" customHeight="1" thickBot="1">
-      <c r="B75" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="C75" s="24"/>
-      <c r="D75" s="25"/>
-      <c r="E75" s="25"/>
-      <c r="F75" s="25"/>
-      <c r="G75" s="25"/>
-    </row>
-    <row r="76" spans="2:7" ht="30" customHeight="1">
-      <c r="B76" s="15" t="s">
+      <c r="C78" s="31"/>
+      <c r="D78" s="31"/>
+      <c r="E78" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="C76" s="26"/>
-      <c r="D76" s="26"/>
-      <c r="E76" s="79" t="s">
-        <v>38</v>
-      </c>
-      <c r="F76" s="80"/>
-      <c r="G76" s="81"/>
-    </row>
-    <row r="77" spans="2:7" ht="30" customHeight="1">
-      <c r="B77" s="16" t="s">
+      <c r="F78" s="33"/>
+      <c r="G78" s="34"/>
+    </row>
+    <row r="79" spans="2:7" ht="30" customHeight="1">
+      <c r="B79" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C77" s="26"/>
-      <c r="D77" s="26"/>
-      <c r="E77" s="76" t="s">
-        <v>38</v>
-      </c>
-      <c r="F77" s="77"/>
-      <c r="G77" s="78"/>
-    </row>
-    <row r="78" spans="2:7" ht="30" customHeight="1">
-      <c r="B78" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="C78" s="26"/>
-      <c r="D78" s="26"/>
-      <c r="E78" s="76" t="s">
-        <v>38</v>
-      </c>
-      <c r="F78" s="77"/>
-      <c r="G78" s="78"/>
-    </row>
-    <row r="79" spans="2:7" ht="30" customHeight="1">
-      <c r="B79" s="16" t="s">
+      <c r="C79" s="31"/>
+      <c r="D79" s="31"/>
+      <c r="E79" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="F79" s="33"/>
+      <c r="G79" s="34"/>
+    </row>
+    <row r="80" spans="2:7" ht="30" customHeight="1">
+      <c r="B80" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C79" s="26"/>
-      <c r="D79" s="26"/>
-      <c r="E79" s="76" t="s">
-        <v>38</v>
-      </c>
-      <c r="F79" s="77"/>
-      <c r="G79" s="78"/>
-    </row>
-    <row r="80" spans="2:7" ht="30" customHeight="1">
-      <c r="B80" s="16" t="s">
+      <c r="C80" s="31"/>
+      <c r="D80" s="31"/>
+      <c r="E80" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="F80" s="33"/>
+      <c r="G80" s="34"/>
+    </row>
+    <row r="81" spans="2:7" ht="30" customHeight="1">
+      <c r="B81" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C80" s="26"/>
-      <c r="D80" s="26"/>
-      <c r="E80" s="76" t="s">
-        <v>38</v>
-      </c>
-      <c r="F80" s="77"/>
-      <c r="G80" s="78"/>
-    </row>
-    <row r="81" spans="2:7" ht="30" customHeight="1">
-      <c r="B81" s="16" t="s">
+      <c r="C81" s="31"/>
+      <c r="D81" s="31"/>
+      <c r="E81" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="F81" s="33"/>
+      <c r="G81" s="34"/>
+    </row>
+    <row r="82" spans="2:7" ht="30" customHeight="1">
+      <c r="B82" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C81" s="26"/>
-      <c r="D81" s="26"/>
-      <c r="E81" s="76" t="s">
-        <v>38</v>
-      </c>
-      <c r="F81" s="77"/>
-      <c r="G81" s="78"/>
-    </row>
-    <row r="82" spans="2:7" ht="30" customHeight="1">
-      <c r="B82" s="16" t="s">
+      <c r="C82" s="31"/>
+      <c r="D82" s="31"/>
+      <c r="E82" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="F82" s="33"/>
+      <c r="G82" s="34"/>
+    </row>
+    <row r="83" spans="2:7" ht="30" customHeight="1">
+      <c r="B83" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C82" s="26"/>
-      <c r="D82" s="26"/>
-      <c r="E82" s="76" t="s">
-        <v>38</v>
-      </c>
-      <c r="F82" s="77"/>
-      <c r="G82" s="78"/>
-    </row>
-    <row r="83" spans="2:7" ht="30" customHeight="1">
-      <c r="B83" s="16" t="s">
+      <c r="C83" s="31"/>
+      <c r="D83" s="31"/>
+      <c r="E83" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="F83" s="33"/>
+      <c r="G83" s="34"/>
+    </row>
+    <row r="84" spans="2:7" ht="30" customHeight="1">
+      <c r="B84" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="C83" s="26"/>
-      <c r="D83" s="26"/>
-      <c r="E83" s="76" t="s">
-        <v>38</v>
-      </c>
-      <c r="F83" s="77"/>
-      <c r="G83" s="78"/>
-    </row>
-    <row r="84" spans="2:7" ht="30" customHeight="1">
-      <c r="B84" s="16" t="s">
+      <c r="C84" s="31"/>
+      <c r="D84" s="31"/>
+      <c r="E84" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="F84" s="33"/>
+      <c r="G84" s="34"/>
+    </row>
+    <row r="85" spans="2:7" ht="30" customHeight="1">
+      <c r="B85" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C84" s="26"/>
-      <c r="D84" s="26"/>
-      <c r="E84" s="76" t="s">
-        <v>38</v>
-      </c>
-      <c r="F84" s="77"/>
-      <c r="G84" s="78"/>
-    </row>
-    <row r="85" spans="2:7" ht="30" customHeight="1">
-      <c r="B85" s="16" t="s">
+      <c r="C85" s="50"/>
+      <c r="D85" s="35"/>
+      <c r="E85" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="F85" s="33"/>
+      <c r="G85" s="34"/>
+    </row>
+    <row r="86" spans="2:7" ht="30" customHeight="1">
+      <c r="B86" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C85" s="88"/>
-      <c r="D85" s="89"/>
-      <c r="E85" s="76" t="s">
-        <v>38</v>
-      </c>
-      <c r="F85" s="77"/>
-      <c r="G85" s="78"/>
-    </row>
-    <row r="86" spans="2:7" ht="30" customHeight="1">
-      <c r="B86" s="16" t="s">
+      <c r="C86" s="50"/>
+      <c r="D86" s="35"/>
+      <c r="E86" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="F86" s="33"/>
+      <c r="G86" s="34"/>
+    </row>
+    <row r="87" spans="2:7" ht="30" customHeight="1">
+      <c r="B87" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C86" s="88"/>
-      <c r="D86" s="89"/>
-      <c r="E86" s="76" t="s">
-        <v>38</v>
-      </c>
-      <c r="F86" s="77"/>
-      <c r="G86" s="78"/>
-    </row>
-    <row r="87" spans="2:7" ht="30" customHeight="1">
-      <c r="B87" s="16" t="s">
+      <c r="C87" s="31"/>
+      <c r="D87" s="31"/>
+      <c r="E87" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="F87" s="33"/>
+      <c r="G87" s="34"/>
+    </row>
+    <row r="88" spans="2:7" ht="30" customHeight="1">
+      <c r="B88" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C88" s="35"/>
+      <c r="D88" s="36"/>
+      <c r="E88" s="36"/>
+      <c r="F88" s="36"/>
+      <c r="G88" s="37"/>
+    </row>
+    <row r="89" spans="2:7" ht="30" customHeight="1" thickBot="1">
+      <c r="B89" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="C87" s="26"/>
-      <c r="D87" s="26"/>
-      <c r="E87" s="76" t="s">
-        <v>38</v>
-      </c>
-      <c r="F87" s="77"/>
-      <c r="G87" s="78"/>
-    </row>
-    <row r="88" spans="2:7" ht="30" customHeight="1">
-      <c r="B88" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="C88" s="89"/>
-      <c r="D88" s="105"/>
-      <c r="E88" s="105"/>
-      <c r="F88" s="105"/>
-      <c r="G88" s="106"/>
-    </row>
-    <row r="89" spans="2:7" ht="30" customHeight="1" thickBot="1">
-      <c r="B89" s="17" t="s">
+      <c r="C89" s="38"/>
+      <c r="D89" s="39"/>
+      <c r="E89" s="39"/>
+      <c r="F89" s="39"/>
+      <c r="G89" s="40"/>
+    </row>
+    <row r="90" spans="2:7" ht="30" customHeight="1">
+      <c r="B90" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="C90" s="42"/>
+      <c r="D90" s="42"/>
+      <c r="E90" s="42"/>
+      <c r="F90" s="42"/>
+      <c r="G90" s="43"/>
+    </row>
+    <row r="91" spans="2:7" ht="30" customHeight="1">
+      <c r="B91" s="44"/>
+      <c r="C91" s="45"/>
+      <c r="D91" s="45"/>
+      <c r="E91" s="45"/>
+      <c r="F91" s="45"/>
+      <c r="G91" s="46"/>
+    </row>
+    <row r="92" spans="2:7" ht="30" customHeight="1" thickBot="1">
+      <c r="B92" s="47"/>
+      <c r="C92" s="48"/>
+      <c r="D92" s="48"/>
+      <c r="E92" s="48"/>
+      <c r="F92" s="48"/>
+      <c r="G92" s="49"/>
+    </row>
+    <row r="93" spans="2:7">
+      <c r="B93" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="C89" s="107"/>
-      <c r="D89" s="108"/>
-      <c r="E89" s="108"/>
-      <c r="F89" s="108"/>
-      <c r="G89" s="109"/>
-    </row>
-    <row r="90" spans="2:7" ht="30" customHeight="1">
-      <c r="B90" s="110" t="s">
-        <v>3</v>
-      </c>
-      <c r="C90" s="111"/>
-      <c r="D90" s="111"/>
-      <c r="E90" s="111"/>
-      <c r="F90" s="111"/>
-      <c r="G90" s="112"/>
-    </row>
-    <row r="91" spans="2:7" ht="30" customHeight="1">
-      <c r="B91" s="113"/>
-      <c r="C91" s="114"/>
-      <c r="D91" s="114"/>
-      <c r="E91" s="114"/>
-      <c r="F91" s="114"/>
-      <c r="G91" s="115"/>
-    </row>
-    <row r="92" spans="2:7" ht="30" customHeight="1" thickBot="1">
-      <c r="B92" s="116"/>
-      <c r="C92" s="117"/>
-      <c r="D92" s="117"/>
-      <c r="E92" s="117"/>
-      <c r="F92" s="117"/>
-      <c r="G92" s="118"/>
-    </row>
-    <row r="93" spans="2:7">
-      <c r="B93" s="90" t="s">
-        <v>50</v>
-      </c>
-      <c r="C93" s="91"/>
-      <c r="D93" s="92"/>
-      <c r="E93" s="99"/>
-      <c r="F93" s="99"/>
-      <c r="G93" s="100"/>
+      <c r="C93" s="18"/>
+      <c r="D93" s="19"/>
+      <c r="E93" s="25"/>
+      <c r="F93" s="25"/>
+      <c r="G93" s="26"/>
     </row>
     <row r="94" spans="2:7">
-      <c r="B94" s="93"/>
-      <c r="C94" s="94"/>
-      <c r="D94" s="95"/>
-      <c r="E94" s="101"/>
-      <c r="F94" s="101"/>
-      <c r="G94" s="102"/>
+      <c r="B94" s="20"/>
+      <c r="C94" s="118"/>
+      <c r="D94" s="21"/>
+      <c r="E94" s="27"/>
+      <c r="F94" s="27"/>
+      <c r="G94" s="28"/>
     </row>
     <row r="95" spans="2:7" ht="39.6" customHeight="1" thickBot="1">
-      <c r="B95" s="96"/>
-      <c r="C95" s="97"/>
-      <c r="D95" s="98"/>
-      <c r="E95" s="103"/>
-      <c r="F95" s="103"/>
-      <c r="G95" s="104"/>
+      <c r="B95" s="22"/>
+      <c r="C95" s="23"/>
+      <c r="D95" s="24"/>
+      <c r="E95" s="29"/>
+      <c r="F95" s="29"/>
+      <c r="G95" s="30"/>
     </row>
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="83">
-    <mergeCell ref="B93:D95"/>
-    <mergeCell ref="E93:G95"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="E87:G87"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C89:G89"/>
-    <mergeCell ref="B90:G90"/>
-    <mergeCell ref="B91:G92"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="E84:G84"/>
-    <mergeCell ref="E85:G85"/>
-    <mergeCell ref="E86:G86"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="E80:G80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="E81:G81"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="E82:G82"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="E65:G69"/>
-    <mergeCell ref="E70:G74"/>
-    <mergeCell ref="B70:C74"/>
-    <mergeCell ref="D70:D74"/>
-    <mergeCell ref="B60:C64"/>
-    <mergeCell ref="B65:C69"/>
-    <mergeCell ref="E78:G78"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="E83:G83"/>
-    <mergeCell ref="E76:G76"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="E77:G77"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="E79:G79"/>
-    <mergeCell ref="E20:G24"/>
-    <mergeCell ref="E25:G29"/>
-    <mergeCell ref="E30:G34"/>
-    <mergeCell ref="E35:G39"/>
-    <mergeCell ref="D60:D64"/>
-    <mergeCell ref="G7:G9"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E15:G19"/>
+    <mergeCell ref="B75:G75"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="E40:G44"/>
+    <mergeCell ref="E45:G49"/>
+    <mergeCell ref="E50:G54"/>
+    <mergeCell ref="E55:G59"/>
+    <mergeCell ref="E60:G64"/>
+    <mergeCell ref="D45:D49"/>
+    <mergeCell ref="B50:C54"/>
+    <mergeCell ref="D50:D54"/>
+    <mergeCell ref="B55:C59"/>
+    <mergeCell ref="D55:D59"/>
+    <mergeCell ref="B45:C49"/>
+    <mergeCell ref="B40:C44"/>
+    <mergeCell ref="D40:D44"/>
+    <mergeCell ref="B20:C24"/>
+    <mergeCell ref="D20:D24"/>
+    <mergeCell ref="B25:C29"/>
+    <mergeCell ref="D25:D29"/>
+    <mergeCell ref="D65:D69"/>
     <mergeCell ref="B30:C34"/>
     <mergeCell ref="D30:D34"/>
     <mergeCell ref="B35:C39"/>
@@ -3614,42 +3558,58 @@
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="D5:E5"/>
+    <mergeCell ref="G7:G9"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E15:G19"/>
     <mergeCell ref="B15:C19"/>
     <mergeCell ref="D15:D19"/>
-    <mergeCell ref="B20:C24"/>
-    <mergeCell ref="D20:D24"/>
-    <mergeCell ref="B25:C29"/>
-    <mergeCell ref="D25:D29"/>
-    <mergeCell ref="D65:D69"/>
-    <mergeCell ref="B75:G75"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="E40:G44"/>
-    <mergeCell ref="E45:G49"/>
-    <mergeCell ref="E50:G54"/>
-    <mergeCell ref="E55:G59"/>
-    <mergeCell ref="E60:G64"/>
-    <mergeCell ref="D45:D49"/>
-    <mergeCell ref="B50:C54"/>
-    <mergeCell ref="D50:D54"/>
-    <mergeCell ref="B55:C59"/>
-    <mergeCell ref="D55:D59"/>
-    <mergeCell ref="B45:C49"/>
-    <mergeCell ref="B40:C44"/>
-    <mergeCell ref="D40:D44"/>
+    <mergeCell ref="E20:G24"/>
+    <mergeCell ref="E25:G29"/>
+    <mergeCell ref="E30:G34"/>
+    <mergeCell ref="E35:G39"/>
+    <mergeCell ref="D60:D64"/>
+    <mergeCell ref="E78:G78"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="E83:G83"/>
+    <mergeCell ref="E76:G76"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="E77:G77"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="E79:G79"/>
+    <mergeCell ref="E65:G69"/>
+    <mergeCell ref="E70:G74"/>
+    <mergeCell ref="B70:C74"/>
+    <mergeCell ref="D70:D74"/>
+    <mergeCell ref="B60:C64"/>
+    <mergeCell ref="B65:C69"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="E84:G84"/>
+    <mergeCell ref="E85:G85"/>
+    <mergeCell ref="E86:G86"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="E80:G80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="E81:G81"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="E82:G82"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="B93:D95"/>
+    <mergeCell ref="E93:G95"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="E87:G87"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C89:G89"/>
+    <mergeCell ref="B90:G90"/>
+    <mergeCell ref="B91:G92"/>
   </mergeCells>
-  <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G11:G13 D15:D74" xr:uid="{508A4757-596D-473F-858B-A5C02905DC2F}">
-      <formula1>"SI,NO"</formula1>
-    </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5" xr:uid="{01645B9D-795D-47FD-9A1E-A227BBD1E6A1}">
+  <dataValidations count="2">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5 G11:G13" xr:uid="{01645B9D-795D-47FD-9A1E-A227BBD1E6A1}">
       <formula1>44927</formula1>
       <formula2>46387</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C9" xr:uid="{FC9C4E5A-8A53-49E1-8C29-1B8733681132}">
-      <formula1>"Komatsu PC200-8MO, Komatsu PC210-10MO, Caterpillar  966H1, Caterpillar 966H2, Doosan DL320A "</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8" xr:uid="{A8112637-6DAF-486A-ADE0-A0BC0437FB91}">
-      <formula1>"Eider Melendez, Gualberto Albor, Wilfredo Ramirez"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D75:G75" xr:uid="{59E242F2-71F6-4C1F-8338-0EBA0839EA3D}">
       <formula1>"Si, N/A"</formula1>
